--- a/IPM_Vd/Techniki zwalczania dręcza pszczelego a tryb prowadzenia pasieki.xlsx
+++ b/IPM_Vd/Techniki zwalczania dręcza pszczelego a tryb prowadzenia pasieki.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rstyczynski/projects/bez-ula/IPM_Vd/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DEB1E15-08A6-4F42-940E-C31EC8DB89B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8CAA62-C042-D647-8A8D-7ACEA42DB360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="27300" windowHeight="16620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="27300" windowHeight="16620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1 - Techniki zwalczania d" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="69">
   <si>
     <t>Techniki zwalczania dręcza pszczelego</t>
   </si>
@@ -34,9 +35,6 @@
     <t>naturalne</t>
   </si>
   <si>
-    <t>hobbystyczne</t>
-  </si>
-  <si>
     <t>ekologiczne</t>
   </si>
   <si>
@@ -64,9 +62,6 @@
     <t>Dennica z siatką</t>
   </si>
   <si>
-    <t>Dennica z tłuszczem</t>
-  </si>
-  <si>
     <t>Wyłapywanie czerwiu trutowego</t>
   </si>
   <si>
@@ -122,13 +117,124 @@
   </si>
   <si>
     <t>Zioła (tymianek, oregano, rabarbar, wrotycz)</t>
+  </si>
+  <si>
+    <t>organiczna</t>
+  </si>
+  <si>
+    <t>Dennica z wkładką z tłuszczem</t>
+  </si>
+  <si>
+    <t>bez chemiczna</t>
+  </si>
+  <si>
+    <t>Pomiar poziomu infekcji dręczem</t>
+  </si>
+  <si>
+    <t>Flotacja cukrowa, CO2</t>
+  </si>
+  <si>
+    <t>Flotacja alkoholowa</t>
+  </si>
+  <si>
+    <t>Pobudzanie odruchów higienicznych</t>
+  </si>
+  <si>
+    <t>Ramka pracy</t>
+  </si>
+  <si>
+    <t>Fizyczna eliminacja dręcza</t>
+  </si>
+  <si>
+    <t>Musi</t>
+  </si>
+  <si>
+    <t>Powinien</t>
+  </si>
+  <si>
+    <t>Może</t>
+  </si>
+  <si>
+    <t>powinien</t>
+  </si>
+  <si>
+    <t>Odporne rasy pszczół (brak w Polsce!)</t>
+  </si>
+  <si>
+    <t>tymianek</t>
+  </si>
+  <si>
+    <t>oregano</t>
+  </si>
+  <si>
+    <t>rabarbar</t>
+  </si>
+  <si>
+    <t>wrotycz</t>
+  </si>
+  <si>
+    <t>Zioła</t>
+  </si>
+  <si>
+    <t>Naturalni wrogowie pasożytów</t>
+  </si>
+  <si>
+    <t>Przeciwdziałanie rozprzestrzenianiu się chorób</t>
+  </si>
+  <si>
+    <t>Pasieka sacjonarna</t>
+  </si>
+  <si>
+    <t>Lokalne rasy pszczół</t>
+  </si>
+  <si>
+    <t>Selekcja pszczoły odpornej</t>
+  </si>
+  <si>
+    <t>Kontrola czerwienia</t>
+  </si>
+  <si>
+    <t>Węza o ustalonym rozmiarze komórki</t>
+  </si>
+  <si>
+    <t>Ul z naturalnych materiałów</t>
+  </si>
+  <si>
+    <t>Zakarmianie na zimę miodem</t>
+  </si>
+  <si>
+    <t>Sąsiedztwo 3km wolne od pestycydów</t>
+  </si>
+  <si>
+    <t>Substancje syntetyczne w walce z chorobami</t>
+  </si>
+  <si>
+    <t>Substancje organiczne w walce z chorobami</t>
+  </si>
+  <si>
+    <t>Specyfiki z Internetu w walce z chorobami</t>
+  </si>
+  <si>
+    <t>Izolator z ramkami do czerwienia (pułapka)</t>
+  </si>
+  <si>
+    <t>Uszkadzanie pszczół</t>
+  </si>
+  <si>
+    <t>przycinanie skrzydełek matce</t>
+  </si>
+  <si>
+    <t>Podgrzewanie pszczół</t>
+  </si>
+  <si>
+    <t>Kontrolne zabijanie czerwiu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -172,8 +278,25 @@
       <color rgb="FF434343"/>
       <name val="Times Roman"/>
     </font>
+    <font>
+      <sz val="17"/>
+      <color rgb="FF262626"/>
+      <name val="Times Roman"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="17"/>
+      <color theme="1" tint="0.14999847407452621"/>
+      <name val="Times Roman"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="17"/>
+      <color indexed="16"/>
+      <name val="Times Roman"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -216,21 +339,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA0E886"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -250,11 +370,37 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color theme="3" tint="0.79998168889431442"/>
+      </left>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="3" tint="0.79998168889431442"/>
+      </left>
+      <right style="thin">
+        <color theme="3" tint="0.79998168889431442"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEDEDE"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEDEDE"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEDEDE"/>
+      </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
+        <color rgb="FFDEDEDE"/>
       </bottom>
       <diagonal/>
     </border>
@@ -264,47 +410,35 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -313,48 +447,69 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="13">
     <dxf>
       <font>
-        <color theme="0" tint="-0.14996795556505021"/>
+        <color theme="1"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="0.59996337778862885"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor theme="4" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -410,211 +565,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color theme="1"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="0.59996337778862885"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.14996795556505021"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="0.59996337778862885"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.14996795556505021"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="0.59996337778862885"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.14996795556505021"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="0.59996337778862885"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.14996795556505021"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="0.59996337778862885"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.14996795556505021"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor theme="6" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1805,500 +1760,514 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="55.33203125" style="1" customWidth="1"/>
-    <col min="3" max="6" width="12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="16.33203125" style="1"/>
+    <col min="3" max="7" width="12" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="16.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:12" ht="27.75" customHeight="1">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-    </row>
-    <row r="2" spans="1:11" ht="102">
-      <c r="A2" s="12" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+    </row>
+    <row r="2" spans="1:12" ht="98">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="13" t="s">
+    </row>
+    <row r="3" spans="1:12" ht="24.5" customHeight="1">
+      <c r="A3" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="24.5" customHeight="1">
-      <c r="A3" s="10" t="s">
+      <c r="B3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+    </row>
+    <row r="4" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+    </row>
+    <row r="5" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+    </row>
+    <row r="6" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+    </row>
+    <row r="7" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-    </row>
-    <row r="4" spans="1:11" ht="24.25" customHeight="1">
-      <c r="A4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="C7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+    </row>
+    <row r="8" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+    </row>
+    <row r="9" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+    </row>
+    <row r="10" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+    </row>
+    <row r="11" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+    </row>
+    <row r="12" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+    </row>
+    <row r="13" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+    </row>
+    <row r="14" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+    </row>
+    <row r="15" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+    </row>
+    <row r="16" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+    </row>
+    <row r="17" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-    </row>
-    <row r="5" spans="1:11" ht="24.25" customHeight="1">
-      <c r="A5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-    </row>
-    <row r="6" spans="1:11" ht="24.25" customHeight="1">
-      <c r="A6" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-    </row>
-    <row r="7" spans="1:11" ht="24.25" customHeight="1">
-      <c r="A7" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-    </row>
-    <row r="8" spans="1:11" ht="24.25" customHeight="1">
-      <c r="A8" s="7" t="s">
+      <c r="C17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+    </row>
+    <row r="18" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A18" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-    </row>
-    <row r="9" spans="1:11" ht="24.25" customHeight="1">
-      <c r="A9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-    </row>
-    <row r="10" spans="1:11" ht="24.25" customHeight="1">
-      <c r="A10" s="8" t="s">
+      <c r="B18" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+    </row>
+    <row r="19" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+    </row>
+    <row r="20" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-    </row>
-    <row r="11" spans="1:11" ht="24.25" customHeight="1">
-      <c r="A11" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-    </row>
-    <row r="12" spans="1:11" ht="24.25" customHeight="1">
-      <c r="A12" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-    </row>
-    <row r="13" spans="1:11" ht="24.25" customHeight="1">
-      <c r="A13" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-    </row>
-    <row r="14" spans="1:11" ht="24.25" customHeight="1">
-      <c r="A14" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-    </row>
-    <row r="15" spans="1:11" ht="24.25" customHeight="1">
-      <c r="A15" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-    </row>
-    <row r="16" spans="1:11" ht="24.25" customHeight="1">
-      <c r="A16" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-    </row>
-    <row r="17" spans="1:11" ht="24.25" customHeight="1">
-      <c r="A17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-    </row>
-    <row r="18" spans="1:11" ht="24.25" customHeight="1">
-      <c r="A18" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-    </row>
-    <row r="19" spans="1:11" ht="24.25" customHeight="1">
-      <c r="A19" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-    </row>
-    <row r="20" spans="1:11" ht="24.25" customHeight="1">
-      <c r="A20" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
+      <c r="C20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C3:F20">
-    <cfRule type="containsText" dxfId="3" priority="21" operator="containsText" text="może">
+  <conditionalFormatting sqref="C3:G20">
+    <cfRule type="containsText" dxfId="12" priority="21" operator="containsText" text="może">
       <formula>NOT(ISERROR(SEARCH("może",C3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="22" stopIfTrue="1" operator="containsText" text="zakaz">
+    <cfRule type="containsText" dxfId="11" priority="22" stopIfTrue="1" operator="containsText" text="zakaz">
       <formula>NOT(ISERROR(SEARCH("zakaz",C3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="23" stopIfTrue="1" operator="containsText" text="musi">
+    <cfRule type="containsText" dxfId="10" priority="23" stopIfTrue="1" operator="containsText" text="musi">
       <formula>NOT(ISERROR(SEARCH("musi",C3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="24" operator="containsText" text="brak">
+    <cfRule type="containsText" dxfId="9" priority="24" operator="containsText" text="brak">
       <formula>NOT(ISERROR(SEARCH("brak",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2308,4 +2277,1221 @@
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F106C2-52A1-E249-B527-E49BD0F2FCBF}">
+  <dimension ref="A1:L46"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="21.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="65.83203125" style="1" customWidth="1"/>
+    <col min="3" max="7" width="16.5" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="16.33203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="27.75" customHeight="1">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+    </row>
+    <row r="2" spans="1:12" ht="98">
+      <c r="A2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="24.5" customHeight="1">
+      <c r="A3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" s="10"/>
+    </row>
+    <row r="4" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+      <c r="A4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="15"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+    </row>
+    <row r="5" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+      <c r="A5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" s="15"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+    </row>
+    <row r="6" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="14"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+    </row>
+    <row r="7" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1" collapsed="1">
+      <c r="A7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="14"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+    </row>
+    <row r="8" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" s="11"/>
+    </row>
+    <row r="9" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+      <c r="A9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="L9" s="11"/>
+    </row>
+    <row r="10" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="11"/>
+    </row>
+    <row r="11" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="15"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+    </row>
+    <row r="12" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A12" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" s="15"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+    </row>
+    <row r="13" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+      <c r="A13" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" s="15"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+    </row>
+    <row r="14" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+      <c r="A14" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="15"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+    </row>
+    <row r="15" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A15" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="15"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+    </row>
+    <row r="16" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A16" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="15"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+    </row>
+    <row r="17" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A17" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="15"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+    </row>
+    <row r="18" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+      <c r="A18" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="15"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+    </row>
+    <row r="19" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L19" s="11"/>
+    </row>
+    <row r="20" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+      <c r="A20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+    </row>
+    <row r="21" spans="1:12" ht="25" customHeight="1">
+      <c r="A21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+    </row>
+    <row r="22" spans="1:12" ht="25" customHeight="1" outlineLevel="1">
+      <c r="A22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+    </row>
+    <row r="23" spans="1:12" ht="25" customHeight="1" outlineLevel="1">
+      <c r="A23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+    </row>
+    <row r="24" spans="1:12" ht="25" customHeight="1" outlineLevel="1">
+      <c r="A24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+    </row>
+    <row r="25" spans="1:12" ht="25" customHeight="1" outlineLevel="1">
+      <c r="A25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+    </row>
+    <row r="26" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A26" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+    </row>
+    <row r="27" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+      <c r="A27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+    </row>
+    <row r="28" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+      <c r="A28" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+    </row>
+    <row r="29" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+      <c r="A29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+    </row>
+    <row r="30" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A30" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+    </row>
+    <row r="31" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A31" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+    </row>
+    <row r="32" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+      <c r="A32" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+    </row>
+    <row r="33" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+      <c r="A33" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+    </row>
+    <row r="34" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+      <c r="A34" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+    </row>
+    <row r="35" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+      <c r="A35" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+    </row>
+    <row r="36" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A36" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+    </row>
+    <row r="37" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+      <c r="A37" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+    </row>
+    <row r="38" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+      <c r="A38" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+    </row>
+    <row r="39" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+    </row>
+    <row r="40" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+      <c r="A40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+    </row>
+    <row r="41" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+      <c r="A41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+    </row>
+    <row r="42" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+      <c r="A42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+    </row>
+    <row r="43" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+      <c r="A43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+    </row>
+    <row r="44" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A44" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+    </row>
+    <row r="45" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1" collapsed="1">
+      <c r="A45" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+    </row>
+    <row r="46" spans="1:12" ht="24.25" customHeight="1">
+      <c r="A46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="J8 I19:J20 I3:I8 J10:J11 I9:J9 I10:I18 C3:G46">
+    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="może">
+      <formula>NOT(ISERROR(SEARCH("może",C3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="7" priority="7" stopIfTrue="1" operator="containsText" text="zakaz">
+      <formula>NOT(ISERROR(SEARCH("zakaz",C3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="8" stopIfTrue="1" operator="containsText" text="musi">
+      <formula>NOT(ISERROR(SEARCH("musi",C3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="9" operator="containsText" text="brak">
+      <formula>NOT(ISERROR(SEARCH("brak",C3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:K5">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="może">
+      <formula>NOT(ISERROR(SEARCH("może",J3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="3" stopIfTrue="1" operator="containsText" text="zakaz">
+      <formula>NOT(ISERROR(SEARCH("zakaz",J3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="4" stopIfTrue="1" operator="containsText" text="musi">
+      <formula>NOT(ISERROR(SEARCH("musi",J3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="brak">
+      <formula>NOT(ISERROR(SEARCH("brak",J3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:G46">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="powinien">
+      <formula>NOT(ISERROR(SEARCH("powinien",C3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/IPM_Vd/Techniki zwalczania dręcza pszczelego a tryb prowadzenia pasieki.xlsx
+++ b/IPM_Vd/Techniki zwalczania dręcza pszczelego a tryb prowadzenia pasieki.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rstyczynski/projects/bez-ula/IPM_Vd/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8CAA62-C042-D647-8A8D-7ACEA42DB360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A823C2-F133-4446-BCE7-4A2C50D45B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="27300" windowHeight="16620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="70">
   <si>
     <t>Techniki zwalczania dręcza pszczelego</t>
   </si>
@@ -228,6 +228,9 @@
   </si>
   <si>
     <t>Kontrolne zabijanie czerwiu</t>
+  </si>
+  <si>
+    <t>nie powinien</t>
   </si>
 </sst>
 </file>
@@ -502,7 +505,147 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="23">
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.14996795556505021"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="0.59996337778862885"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="0.59996337778862885"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7E79"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.14996795556505021"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="0.59996337778862885"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.14996795556505021"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="7" tint="0.59996337778862885"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="1"/>
@@ -570,46 +713,6 @@
       <fill>
         <patternFill>
           <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="7" tint="0.59996337778862885"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.14996795556505021"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -703,6 +806,7 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
+      <color rgb="FFFF7E79"/>
       <color rgb="FF7AC511"/>
       <color rgb="FFA0C47C"/>
     </mruColors>
@@ -2258,16 +2362,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C3:G20">
-    <cfRule type="containsText" dxfId="12" priority="21" operator="containsText" text="może">
+    <cfRule type="containsText" dxfId="13" priority="21" operator="containsText" text="może">
       <formula>NOT(ISERROR(SEARCH("może",C3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="22" stopIfTrue="1" operator="containsText" text="zakaz">
+    <cfRule type="containsText" dxfId="12" priority="22" stopIfTrue="1" operator="containsText" text="zakaz">
       <formula>NOT(ISERROR(SEARCH("zakaz",C3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="23" stopIfTrue="1" operator="containsText" text="musi">
+    <cfRule type="containsText" dxfId="11" priority="23" stopIfTrue="1" operator="containsText" text="musi">
       <formula>NOT(ISERROR(SEARCH("musi",C3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="24" operator="containsText" text="brak">
+    <cfRule type="containsText" dxfId="10" priority="24" operator="containsText" text="brak">
       <formula>NOT(ISERROR(SEARCH("brak",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2286,7 +2390,7 @@
   <cols>
     <col min="1" max="1" width="21.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="65.83203125" style="1" customWidth="1"/>
-    <col min="3" max="7" width="16.5" style="1" customWidth="1"/>
+    <col min="3" max="7" width="17.6640625" style="1" customWidth="1"/>
     <col min="8" max="16384" width="16.33203125" style="1"/>
   </cols>
   <sheetData>
@@ -2353,7 +2457,7 @@
       </c>
       <c r="L3" s="10"/>
     </row>
-    <row r="4" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+    <row r="4" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
@@ -2379,7 +2483,7 @@
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
     </row>
-    <row r="5" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+    <row r="5" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A5" s="7" t="s">
         <v>6</v>
       </c>
@@ -2405,7 +2509,7 @@
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
     </row>
-    <row r="6" spans="1:12" ht="24.25" customHeight="1">
+    <row r="6" spans="1:12" ht="24.25" customHeight="1" collapsed="1">
       <c r="A6" s="7" t="s">
         <v>6</v>
       </c>
@@ -2431,7 +2535,7 @@
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
     </row>
-    <row r="7" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1" collapsed="1">
+    <row r="7" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
       <c r="A7" s="7" t="s">
         <v>6</v>
       </c>
@@ -2457,7 +2561,7 @@
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
     </row>
-    <row r="8" spans="1:12" ht="24.25" customHeight="1">
+    <row r="8" spans="1:12" ht="24.25" customHeight="1" collapsed="1">
       <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
@@ -2486,7 +2590,7 @@
       </c>
       <c r="L8" s="11"/>
     </row>
-    <row r="9" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+    <row r="9" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A9" s="7" t="s">
         <v>6</v>
       </c>
@@ -2515,7 +2619,7 @@
       </c>
       <c r="L9" s="11"/>
     </row>
-    <row r="10" spans="1:12" ht="24.25" customHeight="1">
+    <row r="10" spans="1:12" ht="24.25" customHeight="1" collapsed="1">
       <c r="A10" s="7" t="s">
         <v>6</v>
       </c>
@@ -2596,7 +2700,7 @@
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
     </row>
-    <row r="13" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+    <row r="13" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A13" s="7" t="s">
         <v>6</v>
       </c>
@@ -2622,7 +2726,7 @@
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
     </row>
-    <row r="14" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+    <row r="14" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A14" s="7" t="s">
         <v>6</v>
       </c>
@@ -2648,7 +2752,7 @@
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
     </row>
-    <row r="15" spans="1:12" ht="24.25" customHeight="1">
+    <row r="15" spans="1:12" ht="24.25" customHeight="1" collapsed="1">
       <c r="A15" s="7" t="s">
         <v>6</v>
       </c>
@@ -2685,16 +2789,16 @@
         <v>29</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="I16" s="15"/>
       <c r="K16" s="11"/>
@@ -2711,22 +2815,22 @@
         <v>28</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="I17" s="15"/>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
     </row>
-    <row r="18" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+    <row r="18" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A18" s="7" t="s">
         <v>6</v>
       </c>
@@ -2752,7 +2856,7 @@
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
     </row>
-    <row r="19" spans="1:12" ht="24.25" customHeight="1">
+    <row r="19" spans="1:12" ht="24.25" customHeight="1" collapsed="1">
       <c r="A19" s="4" t="s">
         <v>16</v>
       </c>
@@ -2781,7 +2885,7 @@
       </c>
       <c r="L19" s="11"/>
     </row>
-    <row r="20" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+    <row r="20" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A20" s="4" t="s">
         <v>16</v>
       </c>
@@ -2808,7 +2912,7 @@
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
     </row>
-    <row r="21" spans="1:12" ht="25" customHeight="1">
+    <row r="21" spans="1:12" ht="25" customHeight="1" collapsed="1">
       <c r="A21" s="4" t="s">
         <v>16</v>
       </c>
@@ -2833,7 +2937,7 @@
       <c r="K21" s="11"/>
       <c r="L21" s="11"/>
     </row>
-    <row r="22" spans="1:12" ht="25" customHeight="1" outlineLevel="1">
+    <row r="22" spans="1:12" ht="25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A22" s="4" t="s">
         <v>16</v>
       </c>
@@ -2858,7 +2962,7 @@
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
     </row>
-    <row r="23" spans="1:12" ht="25" customHeight="1" outlineLevel="1">
+    <row r="23" spans="1:12" ht="25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A23" s="4" t="s">
         <v>16</v>
       </c>
@@ -2883,7 +2987,7 @@
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
     </row>
-    <row r="24" spans="1:12" ht="25" customHeight="1" outlineLevel="1">
+    <row r="24" spans="1:12" ht="25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A24" s="4" t="s">
         <v>16</v>
       </c>
@@ -2908,7 +3012,7 @@
       <c r="K24" s="11"/>
       <c r="L24" s="11"/>
     </row>
-    <row r="25" spans="1:12" ht="25" customHeight="1" outlineLevel="1">
+    <row r="25" spans="1:12" ht="25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A25" s="4" t="s">
         <v>16</v>
       </c>
@@ -2933,7 +3037,7 @@
       <c r="K25" s="11"/>
       <c r="L25" s="11"/>
     </row>
-    <row r="26" spans="1:12" ht="24.25" customHeight="1">
+    <row r="26" spans="1:12" ht="24.25" customHeight="1" collapsed="1">
       <c r="A26" s="5" t="s">
         <v>25</v>
       </c>
@@ -2958,7 +3062,7 @@
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
     </row>
-    <row r="27" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+    <row r="27" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A27" s="5" t="s">
         <v>25</v>
       </c>
@@ -2983,7 +3087,7 @@
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
     </row>
-    <row r="28" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+    <row r="28" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A28" s="5" t="s">
         <v>25</v>
       </c>
@@ -3008,7 +3112,7 @@
       <c r="K28" s="11"/>
       <c r="L28" s="11"/>
     </row>
-    <row r="29" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+    <row r="29" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A29" s="5" t="s">
         <v>25</v>
       </c>
@@ -3033,7 +3137,7 @@
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
     </row>
-    <row r="30" spans="1:12" ht="24.25" customHeight="1">
+    <row r="30" spans="1:12" ht="24.25" customHeight="1" collapsed="1">
       <c r="A30" s="5" t="s">
         <v>25</v>
       </c>
@@ -3083,7 +3187,7 @@
       <c r="K31" s="11"/>
       <c r="L31" s="11"/>
     </row>
-    <row r="32" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+    <row r="32" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A32" s="5" t="s">
         <v>25</v>
       </c>
@@ -3108,7 +3212,7 @@
       <c r="K32" s="11"/>
       <c r="L32" s="11"/>
     </row>
-    <row r="33" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+    <row r="33" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A33" s="5" t="s">
         <v>25</v>
       </c>
@@ -3133,7 +3237,7 @@
       <c r="K33" s="11"/>
       <c r="L33" s="11"/>
     </row>
-    <row r="34" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+    <row r="34" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A34" s="5" t="s">
         <v>25</v>
       </c>
@@ -3158,7 +3262,7 @@
       <c r="K34" s="11"/>
       <c r="L34" s="11"/>
     </row>
-    <row r="35" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+    <row r="35" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A35" s="5" t="s">
         <v>25</v>
       </c>
@@ -3183,7 +3287,7 @@
       <c r="K35" s="11"/>
       <c r="L35" s="11"/>
     </row>
-    <row r="36" spans="1:12" ht="24.25" customHeight="1">
+    <row r="36" spans="1:12" ht="24.25" customHeight="1" collapsed="1">
       <c r="A36" s="5" t="s">
         <v>25</v>
       </c>
@@ -3208,7 +3312,7 @@
       <c r="K36" s="11"/>
       <c r="L36" s="11"/>
     </row>
-    <row r="37" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+    <row r="37" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A37" s="5" t="s">
         <v>25</v>
       </c>
@@ -3233,7 +3337,7 @@
       <c r="K37" s="11"/>
       <c r="L37" s="11"/>
     </row>
-    <row r="38" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+    <row r="38" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A38" s="5" t="s">
         <v>25</v>
       </c>
@@ -3258,7 +3362,7 @@
       <c r="K38" s="11"/>
       <c r="L38" s="11"/>
     </row>
-    <row r="39" spans="1:12" ht="24.25" customHeight="1">
+    <row r="39" spans="1:12" ht="24.25" customHeight="1" collapsed="1">
       <c r="A39" s="6" t="s">
         <v>18</v>
       </c>
@@ -3283,7 +3387,7 @@
       <c r="K39" s="11"/>
       <c r="L39" s="11"/>
     </row>
-    <row r="40" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+    <row r="40" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A40" s="6" t="s">
         <v>18</v>
       </c>
@@ -3308,7 +3412,7 @@
       <c r="K40" s="11"/>
       <c r="L40" s="11"/>
     </row>
-    <row r="41" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+    <row r="41" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A41" s="6" t="s">
         <v>18</v>
       </c>
@@ -3333,7 +3437,7 @@
       <c r="K41" s="11"/>
       <c r="L41" s="11"/>
     </row>
-    <row r="42" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+    <row r="42" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A42" s="6" t="s">
         <v>18</v>
       </c>
@@ -3358,7 +3462,7 @@
       <c r="K42" s="11"/>
       <c r="L42" s="11"/>
     </row>
-    <row r="43" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1">
+    <row r="43" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A43" s="6" t="s">
         <v>18</v>
       </c>
@@ -3383,7 +3487,7 @@
       <c r="K43" s="11"/>
       <c r="L43" s="11"/>
     </row>
-    <row r="44" spans="1:12" ht="24.25" customHeight="1">
+    <row r="44" spans="1:12" ht="24.25" customHeight="1" collapsed="1">
       <c r="A44" s="2" t="s">
         <v>22</v>
       </c>
@@ -3408,7 +3512,7 @@
       <c r="K44" s="11"/>
       <c r="L44" s="11"/>
     </row>
-    <row r="45" spans="1:12" ht="24.25" customHeight="1" outlineLevel="1" collapsed="1">
+    <row r="45" spans="1:12" ht="24.25" hidden="1" customHeight="1" outlineLevel="1" collapsed="1">
       <c r="A45" s="2" t="s">
         <v>22</v>
       </c>
@@ -3433,7 +3537,7 @@
       <c r="K45" s="11"/>
       <c r="L45" s="11"/>
     </row>
-    <row r="46" spans="1:12" ht="24.25" customHeight="1">
+    <row r="46" spans="1:12" ht="24.25" customHeight="1" collapsed="1">
       <c r="A46" s="2" t="s">
         <v>22</v>
       </c>
@@ -3459,37 +3563,38 @@
       <c r="L46" s="11"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J8 I19:J20 I3:I8 J10:J11 I9:J9 I10:I18 C3:G46">
-    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="może">
-      <formula>NOT(ISERROR(SEARCH("może",C3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="7" stopIfTrue="1" operator="containsText" text="zakaz">
-      <formula>NOT(ISERROR(SEARCH("zakaz",C3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="8" stopIfTrue="1" operator="containsText" text="musi">
-      <formula>NOT(ISERROR(SEARCH("musi",C3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="9" operator="containsText" text="brak">
-      <formula>NOT(ISERROR(SEARCH("brak",C3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J3:K5">
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="może">
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="może">
       <formula>NOT(ISERROR(SEARCH("może",J3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="3" stopIfTrue="1" operator="containsText" text="zakaz">
+    <cfRule type="containsText" dxfId="8" priority="4" stopIfTrue="1" operator="containsText" text="zakaz">
       <formula>NOT(ISERROR(SEARCH("zakaz",J3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" stopIfTrue="1" operator="containsText" text="musi">
+    <cfRule type="containsText" dxfId="7" priority="5" stopIfTrue="1" operator="containsText" text="musi">
       <formula>NOT(ISERROR(SEARCH("musi",J3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="brak">
+    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="brak">
       <formula>NOT(ISERROR(SEARCH("brak",J3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:G46">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="powinien">
-      <formula>NOT(ISERROR(SEARCH("powinien",C3)))</formula>
+    <cfRule type="containsText" dxfId="5" priority="1" stopIfTrue="1" operator="containsText" text="nie powinien">
+      <formula>NOT(ISERROR(SEARCH("nie powinien",C3)))</formula>
+    </cfRule>
+    <cfRule type="beginsWith" dxfId="4" priority="2" operator="beginsWith" text="powinien">
+      <formula>LEFT(C3,LEN("powinien"))="powinien"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="może">
+      <formula>NOT(ISERROR(SEARCH("może",C3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="8" operator="containsText" text="zakaz">
+      <formula>NOT(ISERROR(SEARCH("zakaz",C3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="9" operator="containsText" text="musi">
+      <formula>NOT(ISERROR(SEARCH("musi",C3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="10" operator="containsText" text="brak">
+      <formula>NOT(ISERROR(SEARCH("brak",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
